--- a/public/planilhas/06_gestao_de_tarefas_kanban.xlsx
+++ b/public/planilhas/06_gestao_de_tarefas_kanban.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RESUMO" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DASHBOARD" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TAREFAS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
@@ -21,7 +21,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,12 +32,18 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="000A1322"/>
-      <sz val="18"/>
+      <color rgb="00C99C66"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
-      <color rgb="005C6B82"/>
+      <b val="1"/>
+      <color rgb="000A1322"/>
+      <sz val="20"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="008593A8"/>
       <sz val="11"/>
     </font>
     <font>
@@ -47,7 +53,34 @@
       <sz val="11"/>
     </font>
     <font>
+      <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="008593A8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="000A1322"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00991B1B"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="008593A8"/>
     </font>
   </fonts>
   <fills count="4">
@@ -64,7 +97,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F6F1EA"/>
+        <fgColor rgb="00F8F4EE"/>
       </patternFill>
     </fill>
   </fills>
@@ -78,37 +111,47 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </left>
       <right style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </right>
       <top style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </top>
       <bottom style="thin">
-        <color rgb="00D0D7DE"/>
+        <color rgb="00E5E7EB"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -120,13 +163,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00DBEAFE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00FFFFFF"/>
         </patternFill>
       </fill>
     </dxf>
@@ -215,6 +251,115 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Distribuição Kanban</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'DASHBOARD'!B11</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'DASHBOARD'!$A$12:$A$14</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'DASHBOARD'!$B$12:$B$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>4</col>
+      <colOff>0</colOff>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4320000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -506,110 +651,189 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trust Excel · Kanban Resumo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>TRUST EXCEL  ·  TRUST CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Contadores automáticos da operação</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+          <t>Dashboard Kanban</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Contadores, WIP e ritmo da operação</t>
+        </is>
+      </c>
+    </row>
+    <row r="4"/>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>A FAZER</t>
+        </is>
+      </c>
+      <c r="B5" s="5">
+        <f>COUNTIF(TAREFAS!D:D,"A fazer")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>FAZENDO</t>
+        </is>
+      </c>
+      <c r="D5" s="5">
+        <f>COUNTIF(TAREFAS!D:D,"Fazendo")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>FEITO</t>
+        </is>
+      </c>
+      <c r="F5" s="5">
+        <f>COUNTIF(TAREFAS!D:D,"Feito")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6"/>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>ATRASADAS</t>
+        </is>
+      </c>
+      <c r="B7" s="6">
+        <f>COUNTIFS(TAREFAS!D:D,"&lt;&gt;Feito",TAREFAS!E:E,"&lt;"&amp;TODAY())</f>
+        <v/>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>FEITAS NA SEMANA</t>
+        </is>
+      </c>
+      <c r="D7" s="5">
+        <f>COUNTIFS(TAREFAS!D:D,"Feito",TAREFAS!G:G,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1)</f>
+        <v/>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>WIP STATUS</t>
+        </is>
+      </c>
+      <c r="F7" s="7">
+        <f>IF(D5&gt;3,"⚠ Acima do limite","✓ Dentro do limite")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>QUADRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>Coluna</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Qtd</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Barra</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="B4" s="4">
-        <f>COUNTIF(TAREFAS!D:D,"A fazer")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="B12" s="10">
+        <f>B5</f>
+        <v/>
+      </c>
+      <c r="C12" s="10">
+        <f>REPT("█",B12)&amp;REPT("░",MAX(0,8-B12))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Fazendo</t>
         </is>
       </c>
-      <c r="B5" s="4">
-        <f>COUNTIF(TAREFAS!D:D,"Fazendo")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="B13" s="10">
+        <f>D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="10">
+        <f>REPT("█",B13)&amp;REPT("░",MAX(0,8-B13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
         <is>
           <t>Feito</t>
         </is>
       </c>
-      <c r="B6" s="4">
-        <f>COUNTIF(TAREFAS!D:D,"Feito")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>Atrasadas agora</t>
-        </is>
-      </c>
-      <c r="B7" s="4">
-        <f>COUNTIFS(TAREFAS!D:D,"&lt;&gt;Feito",TAREFAS!E:E,"&lt;"&amp;TODAY())</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Feitas na semana</t>
-        </is>
-      </c>
-      <c r="B8" s="4">
-        <f>COUNTIFS(TAREFAS!D:D,"Feito",TAREFAS!G:G,"&gt;="&amp;TODAY()-WEEKDAY(TODAY(),2)+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>WIP (Fazendo) — limite sugerido: 3</t>
-        </is>
-      </c>
-      <c r="B9" s="4">
-        <f>IF(B5&gt;3,"⚠ Acima do limite","✓ Dentro do limite")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10"/>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="B14" s="10">
+        <f>F5</f>
+        <v/>
+      </c>
+      <c r="C14" s="10">
+        <f>REPT("█",B14)&amp;REPT("░",MAX(0,8-B14))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Regra de ouro: no máximo 3 tarefas em Fazendo. Se a 4ª quiser entrar, uma tem que sair.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
+  <mergeCells count="3">
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -632,1203 +856,1213 @@
     <col width="29" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="28" customHeight="1">
+    <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Trust Excel · Gestão de Tarefas (Kanban)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
+          <t>TRUST EXCEL  ·  TRUST CORPORATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Gestão de Tarefas (Kanban)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
           <t>Status, prioridade e atraso automático</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+    <row r="4"/>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Tarefa</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Responsável</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>Prioridade</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>Prazo</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t>Alerta</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
+      <c r="G5" s="9" t="inlineStr">
         <is>
           <t>Data conclusão</t>
         </is>
       </c>
-      <c r="H4" s="5" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t>Notas</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>Enviar proposta Cliente A</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Flávio</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D6" s="10" t="inlineStr">
         <is>
           <t>Fazendo</t>
         </is>
       </c>
-      <c r="E5" s="6" t="n">
+      <c r="E6" s="12" t="n">
         <v>46224</v>
       </c>
-      <c r="F5" s="4">
-        <f>IF(A5="","",IF(D5="Feito","",IF(E5&lt;TODAY(),"ATRASADA",IF(E5=TODAY(),"HOJE",""))))</f>
-        <v/>
-      </c>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="inlineStr">
+      <c r="F6" s="10">
+        <f>IF(A6="","",IF(D6="Feito","",IF(E6&lt;TODAY(),"ATRASADA",IF(E6=TODAY(),"HOJE",""))))</f>
+        <v/>
+      </c>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="inlineStr">
         <is>
           <t>Aguardando escopo final</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>Fechar conciliação financeira</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Ana</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
+      <c r="D7" s="10" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="E6" s="6" t="n">
+      <c r="E7" s="12" t="n">
         <v>46226</v>
       </c>
-      <c r="F6" s="4">
-        <f>IF(A6="","",IF(D6="Feito","",IF(E6&lt;TODAY(),"ATRASADA",IF(E6=TODAY(),"HOJE",""))))</f>
-        <v/>
-      </c>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="F7" s="10">
+        <f>IF(A7="","",IF(D7="Feito","",IF(E7&lt;TODAY(),"ATRASADA",IF(E7=TODAY(),"HOJE",""))))</f>
+        <v/>
+      </c>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>Publicar campanha Insta</t>
         </is>
       </c>
-      <c r="B7" s="4" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Time MKT</t>
         </is>
       </c>
-      <c r="C7" s="4" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="D8" s="10" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="E7" s="6" t="n">
+      <c r="E8" s="12" t="n">
         <v>46228</v>
       </c>
-      <c r="F7" s="4">
-        <f>IF(A7="","",IF(D7="Feito","",IF(E7&lt;TODAY(),"ATRASADA",IF(E7=TODAY(),"HOJE",""))))</f>
-        <v/>
-      </c>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="F8" s="10">
+        <f>IF(A8="","",IF(D8="Feito","",IF(E8&lt;TODAY(),"ATRASADA",IF(E8=TODAY(),"HOJE",""))))</f>
+        <v/>
+      </c>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>Revisar contratos abertos</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Jurídico</t>
         </is>
       </c>
-      <c r="C8" s="4" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D8" s="4" t="inlineStr">
+      <c r="D9" s="10" t="inlineStr">
         <is>
           <t>Fazendo</t>
         </is>
       </c>
-      <c r="E8" s="6" t="n">
+      <c r="E9" s="12" t="n">
         <v>46225</v>
       </c>
-      <c r="F8" s="4">
-        <f>IF(A8="","",IF(D8="Feito","",IF(E8&lt;TODAY(),"ATRASADA",IF(E8=TODAY(),"HOJE",""))))</f>
-        <v/>
-      </c>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="F9" s="10">
+        <f>IF(A9="","",IF(D9="Feito","",IF(E9&lt;TODAY(),"ATRASADA",IF(E9=TODAY(),"HOJE",""))))</f>
+        <v/>
+      </c>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Organizar pipeline CRM</t>
         </is>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Comercial</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Média</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Feito</t>
         </is>
       </c>
-      <c r="E9" s="6" t="n">
+      <c r="E10" s="12" t="n">
         <v>46223</v>
       </c>
-      <c r="F9" s="4">
-        <f>IF(A9="","",IF(D9="Feito","",IF(E9&lt;TODAY(),"ATRASADA",IF(E9=TODAY(),"HOJE",""))))</f>
-        <v/>
-      </c>
-      <c r="G9" s="6" t="n">
+      <c r="F10" s="10">
+        <f>IF(A10="","",IF(D10="Feito","",IF(E10&lt;TODAY(),"ATRASADA",IF(E10=TODAY(),"HOJE",""))))</f>
+        <v/>
+      </c>
+      <c r="G10" s="12" t="n">
         <v>46223</v>
       </c>
-      <c r="H9" s="4" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="H10" s="10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>Preparar relatório semanal</t>
         </is>
       </c>
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Ops</t>
         </is>
       </c>
-      <c r="C10" s="4" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>Baixa</t>
         </is>
       </c>
-      <c r="D10" s="4" t="inlineStr">
+      <c r="D11" s="10" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="E10" s="6" t="n">
+      <c r="E11" s="12" t="n">
         <v>46229</v>
       </c>
-      <c r="F10" s="4">
-        <f>IF(A10="","",IF(D10="Feito","",IF(E10&lt;TODAY(),"ATRASADA",IF(E10=TODAY(),"HOJE",""))))</f>
-        <v/>
-      </c>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="F11" s="10">
+        <f>IF(A11="","",IF(D11="Feito","",IF(E11&lt;TODAY(),"ATRASADA",IF(E11=TODAY(),"HOJE",""))))</f>
+        <v/>
+      </c>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Cobrar inadimplentes top 5</t>
         </is>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Financeiro</t>
         </is>
       </c>
-      <c r="C11" s="4" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>Alta</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="D12" s="10" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="E11" s="6" t="n">
+      <c r="E12" s="12" t="n">
         <v>46222</v>
       </c>
-      <c r="F11" s="4">
-        <f>IF(A11="","",IF(D11="Feito","",IF(E11&lt;TODAY(),"ATRASADA",IF(E11=TODAY(),"HOJE",""))))</f>
-        <v/>
-      </c>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="inlineStr">
+      <c r="F12" s="10">
+        <f>IF(A12="","",IF(D12="Feito","",IF(E12&lt;TODAY(),"ATRASADA",IF(E12=TODAY(),"HOJE",""))))</f>
+        <v/>
+      </c>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="inlineStr">
         <is>
           <t>Usar planilha de cobranças</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="n"/>
-      <c r="B12" s="4" t="n"/>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="6" t="n"/>
-      <c r="F12" s="4">
-        <f>IF(A12="","",IF(D12="Feito","",IF(E12&lt;TODAY(),"ATRASADA",IF(E12=TODAY(),"HOJE",""))))</f>
-        <v/>
-      </c>
-      <c r="G12" s="6" t="n"/>
-      <c r="H12" s="4" t="n"/>
-    </row>
     <row r="13">
-      <c r="A13" s="4" t="n"/>
-      <c r="B13" s="4" t="n"/>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="4">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t>Atualizar dashboard TrustCorp</t>
+        </is>
+      </c>
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>Produto</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Média</t>
+        </is>
+      </c>
+      <c r="D13" s="10" t="inlineStr">
+        <is>
+          <t>Fazendo</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="n">
+        <v>46227</v>
+      </c>
+      <c r="F13" s="10">
         <f>IF(A13="","",IF(D13="Feito","",IF(E13&lt;TODAY(),"ATRASADA",IF(E13=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G13" s="6" t="n"/>
-      <c r="H13" s="4" t="n"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="n"/>
-      <c r="B14" s="4" t="n"/>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="6" t="n"/>
-      <c r="F14" s="4">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" s="10" t="n"/>
+      <c r="C14" s="10" t="n"/>
+      <c r="D14" s="10" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="10">
         <f>IF(A14="","",IF(D14="Feito","",IF(E14&lt;TODAY(),"ATRASADA",IF(E14=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="4" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="10" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="n"/>
-      <c r="B15" s="4" t="n"/>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="6" t="n"/>
-      <c r="F15" s="4">
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="10" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="10">
         <f>IF(A15="","",IF(D15="Feito","",IF(E15&lt;TODAY(),"ATRASADA",IF(E15=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="4" t="n"/>
+      <c r="G15" s="12" t="n"/>
+      <c r="H15" s="10" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="n"/>
-      <c r="B16" s="4" t="n"/>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="6" t="n"/>
-      <c r="F16" s="4">
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="10" t="n"/>
+      <c r="C16" s="10" t="n"/>
+      <c r="D16" s="10" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="10">
         <f>IF(A16="","",IF(D16="Feito","",IF(E16&lt;TODAY(),"ATRASADA",IF(E16=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="4" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="10" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="n"/>
-      <c r="B17" s="4" t="n"/>
-      <c r="C17" s="4" t="n"/>
-      <c r="D17" s="4" t="n"/>
-      <c r="E17" s="6" t="n"/>
-      <c r="F17" s="4">
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="10" t="n"/>
+      <c r="C17" s="10" t="n"/>
+      <c r="D17" s="10" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="10">
         <f>IF(A17="","",IF(D17="Feito","",IF(E17&lt;TODAY(),"ATRASADA",IF(E17=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="4" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="10" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="n"/>
-      <c r="B18" s="4" t="n"/>
-      <c r="C18" s="4" t="n"/>
-      <c r="D18" s="4" t="n"/>
-      <c r="E18" s="6" t="n"/>
-      <c r="F18" s="4">
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="10" t="n"/>
+      <c r="C18" s="10" t="n"/>
+      <c r="D18" s="10" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="10">
         <f>IF(A18="","",IF(D18="Feito","",IF(E18&lt;TODAY(),"ATRASADA",IF(E18=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="4" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="10" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="n"/>
-      <c r="B19" s="4" t="n"/>
-      <c r="C19" s="4" t="n"/>
-      <c r="D19" s="4" t="n"/>
-      <c r="E19" s="6" t="n"/>
-      <c r="F19" s="4">
+      <c r="A19" s="10" t="n"/>
+      <c r="B19" s="10" t="n"/>
+      <c r="C19" s="10" t="n"/>
+      <c r="D19" s="10" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="10">
         <f>IF(A19="","",IF(D19="Feito","",IF(E19&lt;TODAY(),"ATRASADA",IF(E19=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="4" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="10" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="n"/>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="4" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="4">
+      <c r="A20" s="10" t="n"/>
+      <c r="B20" s="10" t="n"/>
+      <c r="C20" s="10" t="n"/>
+      <c r="D20" s="10" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="10">
         <f>IF(A20="","",IF(D20="Feito","",IF(E20&lt;TODAY(),"ATRASADA",IF(E20=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="4" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="10" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="n"/>
-      <c r="B21" s="4" t="n"/>
-      <c r="C21" s="4" t="n"/>
-      <c r="D21" s="4" t="n"/>
-      <c r="E21" s="6" t="n"/>
-      <c r="F21" s="4">
+      <c r="A21" s="10" t="n"/>
+      <c r="B21" s="10" t="n"/>
+      <c r="C21" s="10" t="n"/>
+      <c r="D21" s="10" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="10">
         <f>IF(A21="","",IF(D21="Feito","",IF(E21&lt;TODAY(),"ATRASADA",IF(E21=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="4" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="10" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="n"/>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="6" t="n"/>
-      <c r="F22" s="4">
+      <c r="A22" s="10" t="n"/>
+      <c r="B22" s="10" t="n"/>
+      <c r="C22" s="10" t="n"/>
+      <c r="D22" s="10" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="10">
         <f>IF(A22="","",IF(D22="Feito","",IF(E22&lt;TODAY(),"ATRASADA",IF(E22=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="4" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="10" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="n"/>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="6" t="n"/>
-      <c r="F23" s="4">
+      <c r="A23" s="10" t="n"/>
+      <c r="B23" s="10" t="n"/>
+      <c r="C23" s="10" t="n"/>
+      <c r="D23" s="10" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="10">
         <f>IF(A23="","",IF(D23="Feito","",IF(E23&lt;TODAY(),"ATRASADA",IF(E23=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="4" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="10" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="n"/>
-      <c r="B24" s="4" t="n"/>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="6" t="n"/>
-      <c r="F24" s="4">
+      <c r="A24" s="10" t="n"/>
+      <c r="B24" s="10" t="n"/>
+      <c r="C24" s="10" t="n"/>
+      <c r="D24" s="10" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="10">
         <f>IF(A24="","",IF(D24="Feito","",IF(E24&lt;TODAY(),"ATRASADA",IF(E24=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="4" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="10" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="n"/>
-      <c r="B25" s="4" t="n"/>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="6" t="n"/>
-      <c r="F25" s="4">
+      <c r="A25" s="10" t="n"/>
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="10">
         <f>IF(A25="","",IF(D25="Feito","",IF(E25&lt;TODAY(),"ATRASADA",IF(E25=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="4" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="10" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="n"/>
-      <c r="B26" s="4" t="n"/>
-      <c r="C26" s="4" t="n"/>
-      <c r="D26" s="4" t="n"/>
-      <c r="E26" s="6" t="n"/>
-      <c r="F26" s="4">
+      <c r="A26" s="10" t="n"/>
+      <c r="B26" s="10" t="n"/>
+      <c r="C26" s="10" t="n"/>
+      <c r="D26" s="10" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="10">
         <f>IF(A26="","",IF(D26="Feito","",IF(E26&lt;TODAY(),"ATRASADA",IF(E26=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="4" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="10" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="n"/>
-      <c r="B27" s="4" t="n"/>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="6" t="n"/>
-      <c r="F27" s="4">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="10">
         <f>IF(A27="","",IF(D27="Feito","",IF(E27&lt;TODAY(),"ATRASADA",IF(E27=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="4" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="10" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="n"/>
-      <c r="B28" s="4" t="n"/>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="6" t="n"/>
-      <c r="F28" s="4">
+      <c r="A28" s="10" t="n"/>
+      <c r="B28" s="10" t="n"/>
+      <c r="C28" s="10" t="n"/>
+      <c r="D28" s="10" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="10">
         <f>IF(A28="","",IF(D28="Feito","",IF(E28&lt;TODAY(),"ATRASADA",IF(E28=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="4" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="10" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="n"/>
-      <c r="B29" s="4" t="n"/>
-      <c r="C29" s="4" t="n"/>
-      <c r="D29" s="4" t="n"/>
-      <c r="E29" s="6" t="n"/>
-      <c r="F29" s="4">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="10">
         <f>IF(A29="","",IF(D29="Feito","",IF(E29&lt;TODAY(),"ATRASADA",IF(E29=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="4" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="10" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="n"/>
-      <c r="B30" s="4" t="n"/>
-      <c r="C30" s="4" t="n"/>
-      <c r="D30" s="4" t="n"/>
-      <c r="E30" s="6" t="n"/>
-      <c r="F30" s="4">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="10">
         <f>IF(A30="","",IF(D30="Feito","",IF(E30&lt;TODAY(),"ATRASADA",IF(E30=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G30" s="6" t="n"/>
-      <c r="H30" s="4" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="10" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="n"/>
-      <c r="B31" s="4" t="n"/>
-      <c r="C31" s="4" t="n"/>
-      <c r="D31" s="4" t="n"/>
-      <c r="E31" s="6" t="n"/>
-      <c r="F31" s="4">
+      <c r="A31" s="10" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="10" t="n"/>
+      <c r="D31" s="10" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="10">
         <f>IF(A31="","",IF(D31="Feito","",IF(E31&lt;TODAY(),"ATRASADA",IF(E31=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G31" s="6" t="n"/>
-      <c r="H31" s="4" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="10" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="n"/>
-      <c r="B32" s="4" t="n"/>
-      <c r="C32" s="4" t="n"/>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="6" t="n"/>
-      <c r="F32" s="4">
+      <c r="A32" s="10" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="10" t="n"/>
+      <c r="D32" s="10" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="10">
         <f>IF(A32="","",IF(D32="Feito","",IF(E32&lt;TODAY(),"ATRASADA",IF(E32=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G32" s="6" t="n"/>
-      <c r="H32" s="4" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="10" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="n"/>
-      <c r="B33" s="4" t="n"/>
-      <c r="C33" s="4" t="n"/>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="4">
+      <c r="A33" s="10" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="10" t="n"/>
+      <c r="D33" s="10" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="10">
         <f>IF(A33="","",IF(D33="Feito","",IF(E33&lt;TODAY(),"ATRASADA",IF(E33=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="4" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="10" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="n"/>
-      <c r="B34" s="4" t="n"/>
-      <c r="C34" s="4" t="n"/>
-      <c r="D34" s="4" t="n"/>
-      <c r="E34" s="6" t="n"/>
-      <c r="F34" s="4">
+      <c r="A34" s="10" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="10" t="n"/>
+      <c r="D34" s="10" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="10">
         <f>IF(A34="","",IF(D34="Feito","",IF(E34&lt;TODAY(),"ATRASADA",IF(E34=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G34" s="6" t="n"/>
-      <c r="H34" s="4" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="10" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="n"/>
-      <c r="B35" s="4" t="n"/>
-      <c r="C35" s="4" t="n"/>
-      <c r="D35" s="4" t="n"/>
-      <c r="E35" s="6" t="n"/>
-      <c r="F35" s="4">
+      <c r="A35" s="10" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="10" t="n"/>
+      <c r="D35" s="10" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="10">
         <f>IF(A35="","",IF(D35="Feito","",IF(E35&lt;TODAY(),"ATRASADA",IF(E35=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G35" s="6" t="n"/>
-      <c r="H35" s="4" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="10" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="n"/>
-      <c r="B36" s="4" t="n"/>
-      <c r="C36" s="4" t="n"/>
-      <c r="D36" s="4" t="n"/>
-      <c r="E36" s="6" t="n"/>
-      <c r="F36" s="4">
+      <c r="A36" s="10" t="n"/>
+      <c r="B36" s="10" t="n"/>
+      <c r="C36" s="10" t="n"/>
+      <c r="D36" s="10" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="10">
         <f>IF(A36="","",IF(D36="Feito","",IF(E36&lt;TODAY(),"ATRASADA",IF(E36=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G36" s="6" t="n"/>
-      <c r="H36" s="4" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="10" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="n"/>
-      <c r="B37" s="4" t="n"/>
-      <c r="C37" s="4" t="n"/>
-      <c r="D37" s="4" t="n"/>
-      <c r="E37" s="6" t="n"/>
-      <c r="F37" s="4">
+      <c r="A37" s="10" t="n"/>
+      <c r="B37" s="10" t="n"/>
+      <c r="C37" s="10" t="n"/>
+      <c r="D37" s="10" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="10">
         <f>IF(A37="","",IF(D37="Feito","",IF(E37&lt;TODAY(),"ATRASADA",IF(E37=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G37" s="6" t="n"/>
-      <c r="H37" s="4" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="10" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="n"/>
-      <c r="B38" s="4" t="n"/>
-      <c r="C38" s="4" t="n"/>
-      <c r="D38" s="4" t="n"/>
-      <c r="E38" s="6" t="n"/>
-      <c r="F38" s="4">
+      <c r="A38" s="10" t="n"/>
+      <c r="B38" s="10" t="n"/>
+      <c r="C38" s="10" t="n"/>
+      <c r="D38" s="10" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="10">
         <f>IF(A38="","",IF(D38="Feito","",IF(E38&lt;TODAY(),"ATRASADA",IF(E38=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G38" s="6" t="n"/>
-      <c r="H38" s="4" t="n"/>
+      <c r="G38" s="12" t="n"/>
+      <c r="H38" s="10" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="n"/>
-      <c r="B39" s="4" t="n"/>
-      <c r="C39" s="4" t="n"/>
-      <c r="D39" s="4" t="n"/>
-      <c r="E39" s="6" t="n"/>
-      <c r="F39" s="4">
+      <c r="A39" s="10" t="n"/>
+      <c r="B39" s="10" t="n"/>
+      <c r="C39" s="10" t="n"/>
+      <c r="D39" s="10" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="10">
         <f>IF(A39="","",IF(D39="Feito","",IF(E39&lt;TODAY(),"ATRASADA",IF(E39=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G39" s="6" t="n"/>
-      <c r="H39" s="4" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="10" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="n"/>
-      <c r="B40" s="4" t="n"/>
-      <c r="C40" s="4" t="n"/>
-      <c r="D40" s="4" t="n"/>
-      <c r="E40" s="6" t="n"/>
-      <c r="F40" s="4">
+      <c r="A40" s="10" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="10">
         <f>IF(A40="","",IF(D40="Feito","",IF(E40&lt;TODAY(),"ATRASADA",IF(E40=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G40" s="6" t="n"/>
-      <c r="H40" s="4" t="n"/>
+      <c r="G40" s="12" t="n"/>
+      <c r="H40" s="10" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="n"/>
-      <c r="B41" s="4" t="n"/>
-      <c r="C41" s="4" t="n"/>
-      <c r="D41" s="4" t="n"/>
-      <c r="E41" s="6" t="n"/>
-      <c r="F41" s="4">
+      <c r="A41" s="10" t="n"/>
+      <c r="B41" s="10" t="n"/>
+      <c r="C41" s="10" t="n"/>
+      <c r="D41" s="10" t="n"/>
+      <c r="E41" s="12" t="n"/>
+      <c r="F41" s="10">
         <f>IF(A41="","",IF(D41="Feito","",IF(E41&lt;TODAY(),"ATRASADA",IF(E41=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G41" s="6" t="n"/>
-      <c r="H41" s="4" t="n"/>
+      <c r="G41" s="12" t="n"/>
+      <c r="H41" s="10" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="n"/>
-      <c r="B42" s="4" t="n"/>
-      <c r="C42" s="4" t="n"/>
-      <c r="D42" s="4" t="n"/>
-      <c r="E42" s="6" t="n"/>
-      <c r="F42" s="4">
+      <c r="A42" s="10" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="12" t="n"/>
+      <c r="F42" s="10">
         <f>IF(A42="","",IF(D42="Feito","",IF(E42&lt;TODAY(),"ATRASADA",IF(E42=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G42" s="6" t="n"/>
-      <c r="H42" s="4" t="n"/>
+      <c r="G42" s="12" t="n"/>
+      <c r="H42" s="10" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="n"/>
-      <c r="B43" s="4" t="n"/>
-      <c r="C43" s="4" t="n"/>
-      <c r="D43" s="4" t="n"/>
-      <c r="E43" s="6" t="n"/>
-      <c r="F43" s="4">
+      <c r="A43" s="10" t="n"/>
+      <c r="B43" s="10" t="n"/>
+      <c r="C43" s="10" t="n"/>
+      <c r="D43" s="10" t="n"/>
+      <c r="E43" s="12" t="n"/>
+      <c r="F43" s="10">
         <f>IF(A43="","",IF(D43="Feito","",IF(E43&lt;TODAY(),"ATRASADA",IF(E43=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G43" s="6" t="n"/>
-      <c r="H43" s="4" t="n"/>
+      <c r="G43" s="12" t="n"/>
+      <c r="H43" s="10" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="n"/>
-      <c r="B44" s="4" t="n"/>
-      <c r="C44" s="4" t="n"/>
-      <c r="D44" s="4" t="n"/>
-      <c r="E44" s="6" t="n"/>
-      <c r="F44" s="4">
+      <c r="A44" s="10" t="n"/>
+      <c r="B44" s="10" t="n"/>
+      <c r="C44" s="10" t="n"/>
+      <c r="D44" s="10" t="n"/>
+      <c r="E44" s="12" t="n"/>
+      <c r="F44" s="10">
         <f>IF(A44="","",IF(D44="Feito","",IF(E44&lt;TODAY(),"ATRASADA",IF(E44=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G44" s="6" t="n"/>
-      <c r="H44" s="4" t="n"/>
+      <c r="G44" s="12" t="n"/>
+      <c r="H44" s="10" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="n"/>
-      <c r="B45" s="4" t="n"/>
-      <c r="C45" s="4" t="n"/>
-      <c r="D45" s="4" t="n"/>
-      <c r="E45" s="6" t="n"/>
-      <c r="F45" s="4">
+      <c r="A45" s="10" t="n"/>
+      <c r="B45" s="10" t="n"/>
+      <c r="C45" s="10" t="n"/>
+      <c r="D45" s="10" t="n"/>
+      <c r="E45" s="12" t="n"/>
+      <c r="F45" s="10">
         <f>IF(A45="","",IF(D45="Feito","",IF(E45&lt;TODAY(),"ATRASADA",IF(E45=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G45" s="6" t="n"/>
-      <c r="H45" s="4" t="n"/>
+      <c r="G45" s="12" t="n"/>
+      <c r="H45" s="10" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="n"/>
-      <c r="B46" s="4" t="n"/>
-      <c r="C46" s="4" t="n"/>
-      <c r="D46" s="4" t="n"/>
-      <c r="E46" s="6" t="n"/>
-      <c r="F46" s="4">
+      <c r="A46" s="10" t="n"/>
+      <c r="B46" s="10" t="n"/>
+      <c r="C46" s="10" t="n"/>
+      <c r="D46" s="10" t="n"/>
+      <c r="E46" s="12" t="n"/>
+      <c r="F46" s="10">
         <f>IF(A46="","",IF(D46="Feito","",IF(E46&lt;TODAY(),"ATRASADA",IF(E46=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G46" s="6" t="n"/>
-      <c r="H46" s="4" t="n"/>
+      <c r="G46" s="12" t="n"/>
+      <c r="H46" s="10" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="n"/>
-      <c r="B47" s="4" t="n"/>
-      <c r="C47" s="4" t="n"/>
-      <c r="D47" s="4" t="n"/>
-      <c r="E47" s="6" t="n"/>
-      <c r="F47" s="4">
+      <c r="A47" s="10" t="n"/>
+      <c r="B47" s="10" t="n"/>
+      <c r="C47" s="10" t="n"/>
+      <c r="D47" s="10" t="n"/>
+      <c r="E47" s="12" t="n"/>
+      <c r="F47" s="10">
         <f>IF(A47="","",IF(D47="Feito","",IF(E47&lt;TODAY(),"ATRASADA",IF(E47=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G47" s="6" t="n"/>
-      <c r="H47" s="4" t="n"/>
+      <c r="G47" s="12" t="n"/>
+      <c r="H47" s="10" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="n"/>
-      <c r="B48" s="4" t="n"/>
-      <c r="C48" s="4" t="n"/>
-      <c r="D48" s="4" t="n"/>
-      <c r="E48" s="6" t="n"/>
-      <c r="F48" s="4">
+      <c r="A48" s="10" t="n"/>
+      <c r="B48" s="10" t="n"/>
+      <c r="C48" s="10" t="n"/>
+      <c r="D48" s="10" t="n"/>
+      <c r="E48" s="12" t="n"/>
+      <c r="F48" s="10">
         <f>IF(A48="","",IF(D48="Feito","",IF(E48&lt;TODAY(),"ATRASADA",IF(E48=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G48" s="6" t="n"/>
-      <c r="H48" s="4" t="n"/>
+      <c r="G48" s="12" t="n"/>
+      <c r="H48" s="10" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="n"/>
-      <c r="B49" s="4" t="n"/>
-      <c r="C49" s="4" t="n"/>
-      <c r="D49" s="4" t="n"/>
-      <c r="E49" s="6" t="n"/>
-      <c r="F49" s="4">
+      <c r="A49" s="10" t="n"/>
+      <c r="B49" s="10" t="n"/>
+      <c r="C49" s="10" t="n"/>
+      <c r="D49" s="10" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="10">
         <f>IF(A49="","",IF(D49="Feito","",IF(E49&lt;TODAY(),"ATRASADA",IF(E49=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G49" s="6" t="n"/>
-      <c r="H49" s="4" t="n"/>
+      <c r="G49" s="12" t="n"/>
+      <c r="H49" s="10" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="n"/>
-      <c r="B50" s="4" t="n"/>
-      <c r="C50" s="4" t="n"/>
-      <c r="D50" s="4" t="n"/>
-      <c r="E50" s="6" t="n"/>
-      <c r="F50" s="4">
+      <c r="A50" s="10" t="n"/>
+      <c r="B50" s="10" t="n"/>
+      <c r="C50" s="10" t="n"/>
+      <c r="D50" s="10" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="10">
         <f>IF(A50="","",IF(D50="Feito","",IF(E50&lt;TODAY(),"ATRASADA",IF(E50=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="4" t="n"/>
+      <c r="G50" s="12" t="n"/>
+      <c r="H50" s="10" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="n"/>
-      <c r="B51" s="4" t="n"/>
-      <c r="C51" s="4" t="n"/>
-      <c r="D51" s="4" t="n"/>
-      <c r="E51" s="6" t="n"/>
-      <c r="F51" s="4">
+      <c r="A51" s="10" t="n"/>
+      <c r="B51" s="10" t="n"/>
+      <c r="C51" s="10" t="n"/>
+      <c r="D51" s="10" t="n"/>
+      <c r="E51" s="12" t="n"/>
+      <c r="F51" s="10">
         <f>IF(A51="","",IF(D51="Feito","",IF(E51&lt;TODAY(),"ATRASADA",IF(E51=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G51" s="6" t="n"/>
-      <c r="H51" s="4" t="n"/>
+      <c r="G51" s="12" t="n"/>
+      <c r="H51" s="10" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="n"/>
-      <c r="B52" s="4" t="n"/>
-      <c r="C52" s="4" t="n"/>
-      <c r="D52" s="4" t="n"/>
-      <c r="E52" s="6" t="n"/>
-      <c r="F52" s="4">
+      <c r="A52" s="10" t="n"/>
+      <c r="B52" s="10" t="n"/>
+      <c r="C52" s="10" t="n"/>
+      <c r="D52" s="10" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="10">
         <f>IF(A52="","",IF(D52="Feito","",IF(E52&lt;TODAY(),"ATRASADA",IF(E52=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="4" t="n"/>
+      <c r="G52" s="12" t="n"/>
+      <c r="H52" s="10" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="n"/>
-      <c r="B53" s="4" t="n"/>
-      <c r="C53" s="4" t="n"/>
-      <c r="D53" s="4" t="n"/>
-      <c r="E53" s="6" t="n"/>
-      <c r="F53" s="4">
+      <c r="A53" s="10" t="n"/>
+      <c r="B53" s="10" t="n"/>
+      <c r="C53" s="10" t="n"/>
+      <c r="D53" s="10" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="10">
         <f>IF(A53="","",IF(D53="Feito","",IF(E53&lt;TODAY(),"ATRASADA",IF(E53=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G53" s="6" t="n"/>
-      <c r="H53" s="4" t="n"/>
+      <c r="G53" s="12" t="n"/>
+      <c r="H53" s="10" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="n"/>
-      <c r="B54" s="4" t="n"/>
-      <c r="C54" s="4" t="n"/>
-      <c r="D54" s="4" t="n"/>
-      <c r="E54" s="6" t="n"/>
-      <c r="F54" s="4">
+      <c r="A54" s="10" t="n"/>
+      <c r="B54" s="10" t="n"/>
+      <c r="C54" s="10" t="n"/>
+      <c r="D54" s="10" t="n"/>
+      <c r="E54" s="12" t="n"/>
+      <c r="F54" s="10">
         <f>IF(A54="","",IF(D54="Feito","",IF(E54&lt;TODAY(),"ATRASADA",IF(E54=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="4" t="n"/>
+      <c r="G54" s="12" t="n"/>
+      <c r="H54" s="10" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="n"/>
-      <c r="B55" s="4" t="n"/>
-      <c r="C55" s="4" t="n"/>
-      <c r="D55" s="4" t="n"/>
-      <c r="E55" s="6" t="n"/>
-      <c r="F55" s="4">
+      <c r="A55" s="10" t="n"/>
+      <c r="B55" s="10" t="n"/>
+      <c r="C55" s="10" t="n"/>
+      <c r="D55" s="10" t="n"/>
+      <c r="E55" s="12" t="n"/>
+      <c r="F55" s="10">
         <f>IF(A55="","",IF(D55="Feito","",IF(E55&lt;TODAY(),"ATRASADA",IF(E55=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G55" s="6" t="n"/>
-      <c r="H55" s="4" t="n"/>
+      <c r="G55" s="12" t="n"/>
+      <c r="H55" s="10" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="n"/>
-      <c r="B56" s="4" t="n"/>
-      <c r="C56" s="4" t="n"/>
-      <c r="D56" s="4" t="n"/>
-      <c r="E56" s="6" t="n"/>
-      <c r="F56" s="4">
+      <c r="A56" s="10" t="n"/>
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+      <c r="E56" s="12" t="n"/>
+      <c r="F56" s="10">
         <f>IF(A56="","",IF(D56="Feito","",IF(E56&lt;TODAY(),"ATRASADA",IF(E56=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="4" t="n"/>
+      <c r="G56" s="12" t="n"/>
+      <c r="H56" s="10" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="n"/>
-      <c r="B57" s="4" t="n"/>
-      <c r="C57" s="4" t="n"/>
-      <c r="D57" s="4" t="n"/>
-      <c r="E57" s="6" t="n"/>
-      <c r="F57" s="4">
+      <c r="A57" s="10" t="n"/>
+      <c r="B57" s="10" t="n"/>
+      <c r="C57" s="10" t="n"/>
+      <c r="D57" s="10" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="10">
         <f>IF(A57="","",IF(D57="Feito","",IF(E57&lt;TODAY(),"ATRASADA",IF(E57=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G57" s="6" t="n"/>
-      <c r="H57" s="4" t="n"/>
+      <c r="G57" s="12" t="n"/>
+      <c r="H57" s="10" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="n"/>
-      <c r="B58" s="4" t="n"/>
-      <c r="C58" s="4" t="n"/>
-      <c r="D58" s="4" t="n"/>
-      <c r="E58" s="6" t="n"/>
-      <c r="F58" s="4">
+      <c r="A58" s="10" t="n"/>
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="10">
         <f>IF(A58="","",IF(D58="Feito","",IF(E58&lt;TODAY(),"ATRASADA",IF(E58=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="4" t="n"/>
+      <c r="G58" s="12" t="n"/>
+      <c r="H58" s="10" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="n"/>
-      <c r="B59" s="4" t="n"/>
-      <c r="C59" s="4" t="n"/>
-      <c r="D59" s="4" t="n"/>
-      <c r="E59" s="6" t="n"/>
-      <c r="F59" s="4">
+      <c r="A59" s="10" t="n"/>
+      <c r="B59" s="10" t="n"/>
+      <c r="C59" s="10" t="n"/>
+      <c r="D59" s="10" t="n"/>
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="10">
         <f>IF(A59="","",IF(D59="Feito","",IF(E59&lt;TODAY(),"ATRASADA",IF(E59=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G59" s="6" t="n"/>
-      <c r="H59" s="4" t="n"/>
+      <c r="G59" s="12" t="n"/>
+      <c r="H59" s="10" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="n"/>
-      <c r="B60" s="4" t="n"/>
-      <c r="C60" s="4" t="n"/>
-      <c r="D60" s="4" t="n"/>
-      <c r="E60" s="6" t="n"/>
-      <c r="F60" s="4">
+      <c r="A60" s="10" t="n"/>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="10">
         <f>IF(A60="","",IF(D60="Feito","",IF(E60&lt;TODAY(),"ATRASADA",IF(E60=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="4" t="n"/>
+      <c r="G60" s="12" t="n"/>
+      <c r="H60" s="10" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="n"/>
-      <c r="B61" s="4" t="n"/>
-      <c r="C61" s="4" t="n"/>
-      <c r="D61" s="4" t="n"/>
-      <c r="E61" s="6" t="n"/>
-      <c r="F61" s="4">
+      <c r="A61" s="10" t="n"/>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="10">
         <f>IF(A61="","",IF(D61="Feito","",IF(E61&lt;TODAY(),"ATRASADA",IF(E61=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="4" t="n"/>
+      <c r="G61" s="12" t="n"/>
+      <c r="H61" s="10" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="n"/>
-      <c r="B62" s="4" t="n"/>
-      <c r="C62" s="4" t="n"/>
-      <c r="D62" s="4" t="n"/>
-      <c r="E62" s="6" t="n"/>
-      <c r="F62" s="4">
+      <c r="A62" s="10" t="n"/>
+      <c r="B62" s="10" t="n"/>
+      <c r="C62" s="10" t="n"/>
+      <c r="D62" s="10" t="n"/>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="10">
         <f>IF(A62="","",IF(D62="Feito","",IF(E62&lt;TODAY(),"ATRASADA",IF(E62=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G62" s="6" t="n"/>
-      <c r="H62" s="4" t="n"/>
+      <c r="G62" s="12" t="n"/>
+      <c r="H62" s="10" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="n"/>
-      <c r="B63" s="4" t="n"/>
-      <c r="C63" s="4" t="n"/>
-      <c r="D63" s="4" t="n"/>
-      <c r="E63" s="6" t="n"/>
-      <c r="F63" s="4">
+      <c r="A63" s="10" t="n"/>
+      <c r="B63" s="10" t="n"/>
+      <c r="C63" s="10" t="n"/>
+      <c r="D63" s="10" t="n"/>
+      <c r="E63" s="12" t="n"/>
+      <c r="F63" s="10">
         <f>IF(A63="","",IF(D63="Feito","",IF(E63&lt;TODAY(),"ATRASADA",IF(E63=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G63" s="6" t="n"/>
-      <c r="H63" s="4" t="n"/>
+      <c r="G63" s="12" t="n"/>
+      <c r="H63" s="10" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="4" t="n"/>
-      <c r="B64" s="4" t="n"/>
-      <c r="C64" s="4" t="n"/>
-      <c r="D64" s="4" t="n"/>
-      <c r="E64" s="6" t="n"/>
-      <c r="F64" s="4">
+      <c r="A64" s="10" t="n"/>
+      <c r="B64" s="10" t="n"/>
+      <c r="C64" s="10" t="n"/>
+      <c r="D64" s="10" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="10">
         <f>IF(A64="","",IF(D64="Feito","",IF(E64&lt;TODAY(),"ATRASADA",IF(E64=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G64" s="6" t="n"/>
-      <c r="H64" s="4" t="n"/>
+      <c r="G64" s="12" t="n"/>
+      <c r="H64" s="10" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="4" t="n"/>
-      <c r="B65" s="4" t="n"/>
-      <c r="C65" s="4" t="n"/>
-      <c r="D65" s="4" t="n"/>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="4">
+      <c r="A65" s="10" t="n"/>
+      <c r="B65" s="10" t="n"/>
+      <c r="C65" s="10" t="n"/>
+      <c r="D65" s="10" t="n"/>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="10">
         <f>IF(A65="","",IF(D65="Feito","",IF(E65&lt;TODAY(),"ATRASADA",IF(E65=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="4" t="n"/>
+      <c r="G65" s="12" t="n"/>
+      <c r="H65" s="10" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="4" t="n"/>
-      <c r="B66" s="4" t="n"/>
-      <c r="C66" s="4" t="n"/>
-      <c r="D66" s="4" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="4">
+      <c r="A66" s="10" t="n"/>
+      <c r="B66" s="10" t="n"/>
+      <c r="C66" s="10" t="n"/>
+      <c r="D66" s="10" t="n"/>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="10">
         <f>IF(A66="","",IF(D66="Feito","",IF(E66&lt;TODAY(),"ATRASADA",IF(E66=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="4" t="n"/>
+      <c r="G66" s="12" t="n"/>
+      <c r="H66" s="10" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="4" t="n"/>
-      <c r="B67" s="4" t="n"/>
-      <c r="C67" s="4" t="n"/>
-      <c r="D67" s="4" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="4">
+      <c r="A67" s="10" t="n"/>
+      <c r="B67" s="10" t="n"/>
+      <c r="C67" s="10" t="n"/>
+      <c r="D67" s="10" t="n"/>
+      <c r="E67" s="12" t="n"/>
+      <c r="F67" s="10">
         <f>IF(A67="","",IF(D67="Feito","",IF(E67&lt;TODAY(),"ATRASADA",IF(E67=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G67" s="6" t="n"/>
-      <c r="H67" s="4" t="n"/>
+      <c r="G67" s="12" t="n"/>
+      <c r="H67" s="10" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="4" t="n"/>
-      <c r="B68" s="4" t="n"/>
-      <c r="C68" s="4" t="n"/>
-      <c r="D68" s="4" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="4">
+      <c r="A68" s="10" t="n"/>
+      <c r="B68" s="10" t="n"/>
+      <c r="C68" s="10" t="n"/>
+      <c r="D68" s="10" t="n"/>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="10">
         <f>IF(A68="","",IF(D68="Feito","",IF(E68&lt;TODAY(),"ATRASADA",IF(E68=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G68" s="6" t="n"/>
-      <c r="H68" s="4" t="n"/>
+      <c r="G68" s="12" t="n"/>
+      <c r="H68" s="10" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="4" t="n"/>
-      <c r="B69" s="4" t="n"/>
-      <c r="C69" s="4" t="n"/>
-      <c r="D69" s="4" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="4">
+      <c r="A69" s="10" t="n"/>
+      <c r="B69" s="10" t="n"/>
+      <c r="C69" s="10" t="n"/>
+      <c r="D69" s="10" t="n"/>
+      <c r="E69" s="12" t="n"/>
+      <c r="F69" s="10">
         <f>IF(A69="","",IF(D69="Feito","",IF(E69&lt;TODAY(),"ATRASADA",IF(E69=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G69" s="6" t="n"/>
-      <c r="H69" s="4" t="n"/>
+      <c r="G69" s="12" t="n"/>
+      <c r="H69" s="10" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="4" t="n"/>
-      <c r="B70" s="4" t="n"/>
-      <c r="C70" s="4" t="n"/>
-      <c r="D70" s="4" t="n"/>
-      <c r="E70" s="6" t="n"/>
-      <c r="F70" s="4">
+      <c r="A70" s="10" t="n"/>
+      <c r="B70" s="10" t="n"/>
+      <c r="C70" s="10" t="n"/>
+      <c r="D70" s="10" t="n"/>
+      <c r="E70" s="12" t="n"/>
+      <c r="F70" s="10">
         <f>IF(A70="","",IF(D70="Feito","",IF(E70&lt;TODAY(),"ATRASADA",IF(E70=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G70" s="6" t="n"/>
-      <c r="H70" s="4" t="n"/>
+      <c r="G70" s="12" t="n"/>
+      <c r="H70" s="10" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="4" t="n"/>
-      <c r="B71" s="4" t="n"/>
-      <c r="C71" s="4" t="n"/>
-      <c r="D71" s="4" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="4">
+      <c r="A71" s="10" t="n"/>
+      <c r="B71" s="10" t="n"/>
+      <c r="C71" s="10" t="n"/>
+      <c r="D71" s="10" t="n"/>
+      <c r="E71" s="12" t="n"/>
+      <c r="F71" s="10">
         <f>IF(A71="","",IF(D71="Feito","",IF(E71&lt;TODAY(),"ATRASADA",IF(E71=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="4" t="n"/>
+      <c r="G71" s="12" t="n"/>
+      <c r="H71" s="10" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="4" t="n"/>
-      <c r="B72" s="4" t="n"/>
-      <c r="C72" s="4" t="n"/>
-      <c r="D72" s="4" t="n"/>
-      <c r="E72" s="6" t="n"/>
-      <c r="F72" s="4">
+      <c r="A72" s="10" t="n"/>
+      <c r="B72" s="10" t="n"/>
+      <c r="C72" s="10" t="n"/>
+      <c r="D72" s="10" t="n"/>
+      <c r="E72" s="12" t="n"/>
+      <c r="F72" s="10">
         <f>IF(A72="","",IF(D72="Feito","",IF(E72&lt;TODAY(),"ATRASADA",IF(E72=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G72" s="6" t="n"/>
-      <c r="H72" s="4" t="n"/>
+      <c r="G72" s="12" t="n"/>
+      <c r="H72" s="10" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="4" t="n"/>
-      <c r="B73" s="4" t="n"/>
-      <c r="C73" s="4" t="n"/>
-      <c r="D73" s="4" t="n"/>
-      <c r="E73" s="6" t="n"/>
-      <c r="F73" s="4">
+      <c r="A73" s="10" t="n"/>
+      <c r="B73" s="10" t="n"/>
+      <c r="C73" s="10" t="n"/>
+      <c r="D73" s="10" t="n"/>
+      <c r="E73" s="12" t="n"/>
+      <c r="F73" s="10">
         <f>IF(A73="","",IF(D73="Feito","",IF(E73&lt;TODAY(),"ATRASADA",IF(E73=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G73" s="6" t="n"/>
-      <c r="H73" s="4" t="n"/>
+      <c r="G73" s="12" t="n"/>
+      <c r="H73" s="10" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="4" t="n"/>
-      <c r="B74" s="4" t="n"/>
-      <c r="C74" s="4" t="n"/>
-      <c r="D74" s="4" t="n"/>
-      <c r="E74" s="6" t="n"/>
-      <c r="F74" s="4">
+      <c r="A74" s="10" t="n"/>
+      <c r="B74" s="10" t="n"/>
+      <c r="C74" s="10" t="n"/>
+      <c r="D74" s="10" t="n"/>
+      <c r="E74" s="12" t="n"/>
+      <c r="F74" s="10">
         <f>IF(A74="","",IF(D74="Feito","",IF(E74&lt;TODAY(),"ATRASADA",IF(E74=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G74" s="6" t="n"/>
-      <c r="H74" s="4" t="n"/>
+      <c r="G74" s="12" t="n"/>
+      <c r="H74" s="10" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="4" t="n"/>
-      <c r="B75" s="4" t="n"/>
-      <c r="C75" s="4" t="n"/>
-      <c r="D75" s="4" t="n"/>
-      <c r="E75" s="6" t="n"/>
-      <c r="F75" s="4">
+      <c r="A75" s="10" t="n"/>
+      <c r="B75" s="10" t="n"/>
+      <c r="C75" s="10" t="n"/>
+      <c r="D75" s="10" t="n"/>
+      <c r="E75" s="12" t="n"/>
+      <c r="F75" s="10">
         <f>IF(A75="","",IF(D75="Feito","",IF(E75&lt;TODAY(),"ATRASADA",IF(E75=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G75" s="6" t="n"/>
-      <c r="H75" s="4" t="n"/>
+      <c r="G75" s="12" t="n"/>
+      <c r="H75" s="10" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="4" t="n"/>
-      <c r="B76" s="4" t="n"/>
-      <c r="C76" s="4" t="n"/>
-      <c r="D76" s="4" t="n"/>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="4">
+      <c r="A76" s="10" t="n"/>
+      <c r="B76" s="10" t="n"/>
+      <c r="C76" s="10" t="n"/>
+      <c r="D76" s="10" t="n"/>
+      <c r="E76" s="12" t="n"/>
+      <c r="F76" s="10">
         <f>IF(A76="","",IF(D76="Feito","",IF(E76&lt;TODAY(),"ATRASADA",IF(E76=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G76" s="6" t="n"/>
-      <c r="H76" s="4" t="n"/>
+      <c r="G76" s="12" t="n"/>
+      <c r="H76" s="10" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="4" t="n"/>
-      <c r="B77" s="4" t="n"/>
-      <c r="C77" s="4" t="n"/>
-      <c r="D77" s="4" t="n"/>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="4">
+      <c r="A77" s="10" t="n"/>
+      <c r="B77" s="10" t="n"/>
+      <c r="C77" s="10" t="n"/>
+      <c r="D77" s="10" t="n"/>
+      <c r="E77" s="12" t="n"/>
+      <c r="F77" s="10">
         <f>IF(A77="","",IF(D77="Feito","",IF(E77&lt;TODAY(),"ATRASADA",IF(E77=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="4" t="n"/>
+      <c r="G77" s="12" t="n"/>
+      <c r="H77" s="10" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="4" t="n"/>
-      <c r="B78" s="4" t="n"/>
-      <c r="C78" s="4" t="n"/>
-      <c r="D78" s="4" t="n"/>
-      <c r="E78" s="6" t="n"/>
-      <c r="F78" s="4">
+      <c r="A78" s="10" t="n"/>
+      <c r="B78" s="10" t="n"/>
+      <c r="C78" s="10" t="n"/>
+      <c r="D78" s="10" t="n"/>
+      <c r="E78" s="12" t="n"/>
+      <c r="F78" s="10">
         <f>IF(A78="","",IF(D78="Feito","",IF(E78&lt;TODAY(),"ATRASADA",IF(E78=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G78" s="6" t="n"/>
-      <c r="H78" s="4" t="n"/>
+      <c r="G78" s="12" t="n"/>
+      <c r="H78" s="10" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="4" t="n"/>
-      <c r="B79" s="4" t="n"/>
-      <c r="C79" s="4" t="n"/>
-      <c r="D79" s="4" t="n"/>
-      <c r="E79" s="6" t="n"/>
-      <c r="F79" s="4">
+      <c r="A79" s="10" t="n"/>
+      <c r="B79" s="10" t="n"/>
+      <c r="C79" s="10" t="n"/>
+      <c r="D79" s="10" t="n"/>
+      <c r="E79" s="12" t="n"/>
+      <c r="F79" s="10">
         <f>IF(A79="","",IF(D79="Feito","",IF(E79&lt;TODAY(),"ATRASADA",IF(E79=TODAY(),"HOJE",""))))</f>
         <v/>
       </c>
-      <c r="G79" s="6" t="n"/>
-      <c r="H79" s="4" t="n"/>
+      <c r="G79" s="12" t="n"/>
+      <c r="H79" s="10" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
+    <mergeCell ref="A3:H3"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D5:D200">
+  <conditionalFormatting sqref="D6:D200">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>D5="Feito"</formula>
+      <formula>D6="Feito"</formula>
     </cfRule>
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>D5="Fazendo"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="3" dxfId="2">
-      <formula>D5="A fazer"</formula>
+      <formula>D6="Fazendo"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F5:F200">
+  <conditionalFormatting sqref="F6:F200">
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>F6="ATRASADA"</formula>
+    </cfRule>
     <cfRule type="expression" priority="4" dxfId="3">
-      <formula>F5="ATRASADA"</formula>
-    </cfRule>
-    <cfRule type="expression" priority="5" dxfId="4">
-      <formula>F5="HOJE"</formula>
+      <formula>F6="HOJE"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="C5:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C6:C200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Alta,Média,Baixa"</formula1>
     </dataValidation>
-    <dataValidation sqref="D5:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D6:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"A fazer,Fazendo,Feito"</formula1>
     </dataValidation>
   </dataValidations>
